--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E9599A-75C6-4556-A242-31E5C59ACF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BEFE29-1E26-4691-83F5-79466F4394D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40395" yWindow="3075" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43335" yWindow="2775" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BEFE29-1E26-4691-83F5-79466F4394D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415B14D3-D053-4E06-92EF-FCB05A7DE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43335" yWindow="2775" windowWidth="25935" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47505" yWindow="1260" windowWidth="14940" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="16">
   <si>
     <t>ItemId</t>
   </si>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
@@ -526,108 +526,108 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="A4" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="A5" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="A6" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="A7" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="A8" s="1">
+        <v>1999</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
@@ -687,127 +687,127 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>2009</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>3101</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>3102</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>3103</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>3104</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>3105</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>3106</v>
+        <v>3101</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>10</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>3201</v>
+        <v>3102</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>10</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>3202</v>
+        <v>3103</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>10</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -867,7 +867,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>3203</v>
+        <v>3104</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>10</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>3204</v>
+        <v>3105</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>3205</v>
+        <v>3106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -927,7 +927,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>3206</v>
+        <v>3201</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
@@ -946,122 +946,222 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
+        <v>3202</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>3203</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>3204</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>3205</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>3206</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
         <v>5001</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="D30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
         <v>5002</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="D31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
         <v>6001</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="D32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="F32" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>6002</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="D33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
         <v>6003</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="D34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="F34" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
         <v>6004</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="D35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F35" s="5">
         <v>0</v>
       </c>
     </row>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Equip_System_Package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415B14D3-D053-4E06-92EF-FCB05A7DE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28335DE-FFFF-4659-AA74-365C7A8205C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47505" yWindow="1260" windowWidth="14940" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="19">
   <si>
     <t>ItemId</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Skin</t>
   </si>
   <si>
-    <t>Rare</t>
+    <t>Epic</t>
   </si>
   <si>
     <t>Inventory</t>
@@ -58,13 +58,22 @@
     <t>Equip</t>
   </si>
   <si>
-    <t>Potion</t>
-  </si>
-  <si>
     <t>Uncommon</t>
   </si>
   <si>
-    <t>Epic</t>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>Potion</t>
   </si>
   <si>
     <t>Material</t>
@@ -74,13 +83,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -111,7 +127,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -132,16 +148,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -149,8 +165,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -458,608 +477,608 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="1" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="17.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1001</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="b">
+      <c r="D2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>1002</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="b">
+      <c r="D3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>1003</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="b">
+      <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>1004</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="b">
+      <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>1005</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="b">
+      <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>1006</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="b">
+      <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>1999</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="b">
+      <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>2001</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>2002</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>2003</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>2004</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>2005</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>2006</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>2007</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>2008</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>2009</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>3101</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="A18" s="4">
+        <v>3111</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>3102</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="A19" s="4">
+        <v>3112</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>3103</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="A20" s="4">
+        <v>3113</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>3104</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="A21" s="4">
+        <v>3121</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>3105</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="A22" s="4">
+        <v>3122</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>3106</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="A23" s="4">
+        <v>3123</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>3201</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="A24" s="4">
+        <v>3131</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>3202</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="3">
+      <c r="A25" s="4">
+        <v>3132</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>3203</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="A26" s="4">
+        <v>3133</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>3204</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="A27" s="4">
+        <v>3141</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>3205</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="3">
+      <c r="A28" s="4">
+        <v>3142</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>3206</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="3">
+      <c r="A29" s="4">
+        <v>3143</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>5001</v>
+        <v>3151</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F30" s="4">
         <v>0</v>
@@ -1067,106 +1086,2386 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
+        <v>3152</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>3153</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>3161</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>3162</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>3163</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>3211</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>3212</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>3213</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>3221</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>3222</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>3223</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>3231</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>3232</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>3233</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>3241</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>3242</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>3243</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>3251</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>3252</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>3253</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>3261</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>3262</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>3263</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
+        <v>3311</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>3312</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
+        <v>3313</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>3321</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>3322</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>3323</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
+        <v>3331</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>3332</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
+        <v>3333</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
+        <v>3341</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>3342</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
+        <v>3343</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
+        <v>3351</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
+        <v>3352</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
+        <v>3353</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>3361</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
+        <v>3362</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>3363</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
+        <v>3411</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>3412</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
+        <v>3413</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
+        <v>3421</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
+        <v>3422</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
+        <v>3423</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="4">
+        <v>3431</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
+        <v>3432</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="4">
+        <v>3433</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
+        <v>3441</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
+        <v>3442</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
+        <v>3443</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
+        <v>3451</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
+        <v>3452</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="4">
+        <v>3453</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="4">
+        <v>3461</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="4">
+        <v>3462</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
+        <v>3463</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="4">
+        <v>3511</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
+        <v>3512</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="4">
+        <v>3513</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
+        <v>3521</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="4">
+        <v>3522</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="4">
+        <v>3523</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="4">
+        <v>3531</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="4">
+        <v>3532</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="4">
+        <v>3533</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="4">
+        <v>3541</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="4">
+        <v>3542</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="4">
+        <v>3543</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="4">
+        <v>3551</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
+        <v>3552</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="4">
+        <v>3553</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
+        <v>3561</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="4">
+        <v>3562</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
+        <v>3563</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="4">
+        <v>3611</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="4">
+        <v>3612</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="4">
+        <v>3613</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="4">
+        <v>3621</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="4">
+        <v>3622</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
+        <v>3623</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
+        <v>3631</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
+        <v>3632</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
+        <v>3633</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
+        <v>3641</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
+        <v>3642</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
+        <v>3643</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
+        <v>3651</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
+        <v>3652</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="4">
+        <v>3653</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
+        <v>3661</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="4">
+        <v>3662</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
+        <v>3663</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F125" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="4">
+        <v>3711</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
+        <v>3712</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
+        <v>3713</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F128" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
+        <v>3721</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="4">
+        <v>3722</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F130" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
+        <v>3723</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="4">
+        <v>3731</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
+        <v>3732</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="4">
+        <v>3733</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
+        <v>3741</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="4">
+        <v>3742</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
+        <v>3743</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="4">
+        <v>3751</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
+        <v>3752</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F139" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="4">
+        <v>3753</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F140" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
+        <v>3761</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F141" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="4">
+        <v>3762</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F142" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
+        <v>3763</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F143" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="5">
+        <v>5001</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="5">
         <v>5002</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="B145" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="6">
+        <v>6001</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E146" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="4" t="b">
+      <c r="F146" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="6">
+        <v>6002</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
-        <v>6001</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="5" t="b">
+      <c r="E147" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="6">
+        <v>6003</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
-        <v>6002</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="5" t="b">
+      <c r="E148" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="6">
+        <v>6004</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
-        <v>6003</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
-        <v>6004</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="5">
+      <c r="E149" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Equip_System_Package\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28335DE-FFFF-4659-AA74-365C7A8205C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB8B555-EA61-41B5-AF4E-D0ACA9AFA199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="19">
   <si>
     <t>ItemId</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="9" style="2"/>
@@ -626,7 +626,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>1999</v>
+        <v>1007</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -645,28 +645,28 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>2001</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="A9" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
@@ -726,7 +726,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>8</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
@@ -825,28 +825,28 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>3111</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="A18" s="3">
+        <v>2009</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>10</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>10</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
-        <v>3121</v>
+        <v>3113</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>10</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>10</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>3131</v>
+        <v>3123</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>10</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>3141</v>
+        <v>3133</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>10</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>10</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>10</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>3151</v>
+        <v>3143</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>10</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>10</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>10</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>3161</v>
+        <v>3153</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>10</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>10</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>10</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>3211</v>
+        <v>3163</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>10</v>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>10</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>10</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>3221</v>
+        <v>3213</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>10</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>10</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>10</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>10</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>10</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>10</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>10</v>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>10</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>10</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>10</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>10</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>10</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>10</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>10</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
-        <v>3311</v>
+        <v>3263</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>10</v>
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F54" s="4">
         <v>0</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>10</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>10</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
-        <v>3321</v>
+        <v>3313</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>10</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>10</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>10</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
-        <v>3331</v>
+        <v>3323</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>10</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>10</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>10</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
-        <v>3341</v>
+        <v>3333</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>10</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>10</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>10</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
-        <v>3351</v>
+        <v>3343</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>10</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>10</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>10</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
-        <v>3361</v>
+        <v>3353</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>10</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>10</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>10</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
-        <v>3411</v>
+        <v>3363</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F72" s="4">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>10</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>10</v>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
-        <v>3421</v>
+        <v>3413</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>10</v>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>10</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
-        <v>3431</v>
+        <v>3423</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>10</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
-        <v>3441</v>
+        <v>3433</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>10</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>10</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>10</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
-        <v>3451</v>
+        <v>3443</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>10</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>10</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>10</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>10</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>10</v>
@@ -2246,7 +2246,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>10</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
-        <v>3511</v>
+        <v>3463</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>10</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F90" s="4">
         <v>0</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>10</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>10</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
-        <v>3521</v>
+        <v>3513</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>10</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>10</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
-        <v>3531</v>
+        <v>3523</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>10</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>10</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>10</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
-        <v>3541</v>
+        <v>3533</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>10</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>10</v>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>10</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
-        <v>3551</v>
+        <v>3543</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>10</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>10</v>
@@ -2546,7 +2546,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>10</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
-        <v>3561</v>
+        <v>3553</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>10</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>10</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>10</v>
@@ -2626,7 +2626,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
-        <v>3611</v>
+        <v>3563</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>10</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F108" s="4">
         <v>0</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>10</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>10</v>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
-        <v>3621</v>
+        <v>3613</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>10</v>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>10</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>10</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
-        <v>3631</v>
+        <v>3623</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>10</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>10</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>10</v>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
-        <v>3641</v>
+        <v>3633</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>10</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>10</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>10</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
-        <v>3651</v>
+        <v>3643</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>10</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>10</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
-        <v>3661</v>
+        <v>3653</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>10</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>10</v>
@@ -2966,7 +2966,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>10</v>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
-        <v>3711</v>
+        <v>3663</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>10</v>
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F126" s="4">
         <v>0</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>10</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>10</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
-        <v>3721</v>
+        <v>3713</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>10</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>10</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>10</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>10</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>10</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>10</v>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>10</v>
@@ -3206,7 +3206,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>10</v>
@@ -3226,7 +3226,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
-        <v>3751</v>
+        <v>3743</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>10</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>10</v>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>10</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>10</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>10</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>10</v>
@@ -3345,28 +3345,28 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="5">
-        <v>5001</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D144" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="5">
+      <c r="A144" s="4">
+        <v>3763</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F144" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -3385,28 +3385,28 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="6">
-        <v>6001</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D146" s="6" t="b">
+      <c r="A146" s="5">
+        <v>5002</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" s="6">
+      <c r="E146" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>10</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>10</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>10</v>
@@ -3461,6 +3461,26 @@
         <v>12</v>
       </c>
       <c r="F149" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="6">
+        <v>6004</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB8B555-EA61-41B5-AF4E-D0ACA9AFA199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD2415C-F57F-415B-82DA-A2BAA9B24BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20820" yWindow="1275" windowWidth="12675" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="26">
   <si>
     <t>ItemId</t>
   </si>
@@ -78,6 +91,29 @@
   <si>
     <t>Material</t>
   </si>
+  <si>
+    <t>Tier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
 </sst>
 </file>
 
@@ -106,7 +142,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,6 +170,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -165,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -175,6 +217,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -477,14 +520,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="17.25" style="2" customWidth="1"/>
+    <col min="1" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="17.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,10 +544,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
@@ -520,11 +566,14 @@
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
@@ -540,11 +589,14 @@
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1003</v>
       </c>
@@ -560,11 +612,14 @@
       <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1004</v>
       </c>
@@ -580,11 +635,14 @@
       <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1005</v>
       </c>
@@ -600,11 +658,14 @@
       <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1006</v>
       </c>
@@ -620,11 +681,14 @@
       <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1007</v>
       </c>
@@ -640,11 +704,14 @@
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1999</v>
       </c>
@@ -660,11 +727,14 @@
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2001</v>
       </c>
@@ -680,11 +750,14 @@
       <c r="E10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2002</v>
       </c>
@@ -700,11 +773,14 @@
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>2003</v>
       </c>
@@ -720,11 +796,14 @@
       <c r="E12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>2004</v>
       </c>
@@ -740,11 +819,14 @@
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2005</v>
       </c>
@@ -760,11 +842,14 @@
       <c r="E14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2006</v>
       </c>
@@ -780,11 +865,14 @@
       <c r="E15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>2007</v>
       </c>
@@ -800,11 +888,14 @@
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>2008</v>
       </c>
@@ -820,11 +911,14 @@
       <c r="E17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>2009</v>
       </c>
@@ -840,11 +934,14 @@
       <c r="E18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>3111</v>
       </c>
@@ -860,11 +957,14 @@
       <c r="E19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>3112</v>
       </c>
@@ -880,11 +980,14 @@
       <c r="E20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>3113</v>
       </c>
@@ -900,11 +1003,14 @@
       <c r="E21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>3121</v>
       </c>
@@ -920,11 +1026,14 @@
       <c r="E22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>3122</v>
       </c>
@@ -940,11 +1049,14 @@
       <c r="E23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>3123</v>
       </c>
@@ -960,11 +1072,14 @@
       <c r="E24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>3131</v>
       </c>
@@ -980,11 +1095,14 @@
       <c r="E25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>3132</v>
       </c>
@@ -1000,11 +1118,14 @@
       <c r="E26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>3133</v>
       </c>
@@ -1020,11 +1141,14 @@
       <c r="E27" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>3141</v>
       </c>
@@ -1040,11 +1164,14 @@
       <c r="E28" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>3142</v>
       </c>
@@ -1060,11 +1187,14 @@
       <c r="E29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>3143</v>
       </c>
@@ -1080,11 +1210,14 @@
       <c r="E30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>3151</v>
       </c>
@@ -1100,11 +1233,14 @@
       <c r="E31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>3152</v>
       </c>
@@ -1120,11 +1256,14 @@
       <c r="E32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>3153</v>
       </c>
@@ -1140,11 +1279,14 @@
       <c r="E33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>3161</v>
       </c>
@@ -1160,11 +1302,14 @@
       <c r="E34" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>3162</v>
       </c>
@@ -1180,11 +1325,14 @@
       <c r="E35" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>3163</v>
       </c>
@@ -1200,11 +1348,14 @@
       <c r="E36" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>3211</v>
       </c>
@@ -1220,11 +1371,14 @@
       <c r="E37" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>3212</v>
       </c>
@@ -1240,11 +1394,14 @@
       <c r="E38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>3213</v>
       </c>
@@ -1260,11 +1417,14 @@
       <c r="E39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>3221</v>
       </c>
@@ -1280,11 +1440,14 @@
       <c r="E40" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>3222</v>
       </c>
@@ -1300,11 +1463,14 @@
       <c r="E41" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>3223</v>
       </c>
@@ -1320,11 +1486,14 @@
       <c r="E42" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F42" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>3231</v>
       </c>
@@ -1340,11 +1509,14 @@
       <c r="E43" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>3232</v>
       </c>
@@ -1360,11 +1532,14 @@
       <c r="E44" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>3233</v>
       </c>
@@ -1380,11 +1555,14 @@
       <c r="E45" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F45" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>3241</v>
       </c>
@@ -1400,11 +1578,14 @@
       <c r="E46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>3242</v>
       </c>
@@ -1420,11 +1601,14 @@
       <c r="E47" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>3243</v>
       </c>
@@ -1440,11 +1624,14 @@
       <c r="E48" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F48" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>3251</v>
       </c>
@@ -1460,11 +1647,14 @@
       <c r="E49" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>3252</v>
       </c>
@@ -1480,11 +1670,14 @@
       <c r="E50" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>3253</v>
       </c>
@@ -1500,11 +1693,14 @@
       <c r="E51" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>3261</v>
       </c>
@@ -1520,11 +1716,14 @@
       <c r="E52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F52" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>3262</v>
       </c>
@@ -1540,11 +1739,14 @@
       <c r="E53" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>3263</v>
       </c>
@@ -1560,11 +1762,14 @@
       <c r="E54" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F54" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>3311</v>
       </c>
@@ -1580,11 +1785,14 @@
       <c r="E55" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F55" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>3312</v>
       </c>
@@ -1600,11 +1808,14 @@
       <c r="E56" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F56" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>3313</v>
       </c>
@@ -1620,11 +1831,14 @@
       <c r="E57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>3321</v>
       </c>
@@ -1640,11 +1854,14 @@
       <c r="E58" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F58" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>3322</v>
       </c>
@@ -1660,11 +1877,14 @@
       <c r="E59" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>3323</v>
       </c>
@@ -1680,11 +1900,14 @@
       <c r="E60" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F60" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>3331</v>
       </c>
@@ -1700,11 +1923,14 @@
       <c r="E61" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F61" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>3332</v>
       </c>
@@ -1720,11 +1946,14 @@
       <c r="E62" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F62" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>3333</v>
       </c>
@@ -1740,11 +1969,14 @@
       <c r="E63" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F63" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>3341</v>
       </c>
@@ -1760,11 +1992,14 @@
       <c r="E64" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F64" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>3342</v>
       </c>
@@ -1780,11 +2015,14 @@
       <c r="E65" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>3343</v>
       </c>
@@ -1800,11 +2038,14 @@
       <c r="E66" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F66" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>3351</v>
       </c>
@@ -1820,11 +2061,14 @@
       <c r="E67" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>3352</v>
       </c>
@@ -1840,11 +2084,14 @@
       <c r="E68" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>3353</v>
       </c>
@@ -1860,11 +2107,14 @@
       <c r="E69" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F69" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>3361</v>
       </c>
@@ -1880,11 +2130,14 @@
       <c r="E70" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F70" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>3362</v>
       </c>
@@ -1900,11 +2153,14 @@
       <c r="E71" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F71" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>3363</v>
       </c>
@@ -1920,11 +2176,14 @@
       <c r="E72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F72" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>3411</v>
       </c>
@@ -1940,11 +2199,14 @@
       <c r="E73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F73" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>3412</v>
       </c>
@@ -1960,11 +2222,14 @@
       <c r="E74" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>3413</v>
       </c>
@@ -1980,11 +2245,14 @@
       <c r="E75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F75" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>3421</v>
       </c>
@@ -2000,11 +2268,14 @@
       <c r="E76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F76" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F76" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>3422</v>
       </c>
@@ -2020,11 +2291,14 @@
       <c r="E77" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>3423</v>
       </c>
@@ -2040,11 +2314,14 @@
       <c r="E78" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F78" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>3431</v>
       </c>
@@ -2060,11 +2337,14 @@
       <c r="E79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F79" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F79" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>3432</v>
       </c>
@@ -2080,11 +2360,14 @@
       <c r="E80" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F80" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F80" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>3433</v>
       </c>
@@ -2100,11 +2383,14 @@
       <c r="E81" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F81" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F81" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>3441</v>
       </c>
@@ -2120,11 +2406,14 @@
       <c r="E82" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F82" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F82" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>3442</v>
       </c>
@@ -2140,11 +2429,14 @@
       <c r="E83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F83" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>3443</v>
       </c>
@@ -2160,11 +2452,14 @@
       <c r="E84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F84" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F84" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>3451</v>
       </c>
@@ -2180,11 +2475,14 @@
       <c r="E85" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F85" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>3452</v>
       </c>
@@ -2200,11 +2498,14 @@
       <c r="E86" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F86" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F86" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>3453</v>
       </c>
@@ -2220,11 +2521,14 @@
       <c r="E87" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F87" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>3461</v>
       </c>
@@ -2240,11 +2544,14 @@
       <c r="E88" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F88" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>3462</v>
       </c>
@@ -2260,11 +2567,14 @@
       <c r="E89" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F89" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F89" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>3463</v>
       </c>
@@ -2280,11 +2590,14 @@
       <c r="E90" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F90" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F90" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>3511</v>
       </c>
@@ -2300,11 +2613,14 @@
       <c r="E91" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F91" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F91" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>3512</v>
       </c>
@@ -2320,11 +2636,14 @@
       <c r="E92" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F92" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F92" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>3513</v>
       </c>
@@ -2340,11 +2659,14 @@
       <c r="E93" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F93" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F93" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>3521</v>
       </c>
@@ -2360,11 +2682,14 @@
       <c r="E94" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F94" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>3522</v>
       </c>
@@ -2380,11 +2705,14 @@
       <c r="E95" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F95" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F95" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>3523</v>
       </c>
@@ -2400,11 +2728,14 @@
       <c r="E96" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F96" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F96" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>3531</v>
       </c>
@@ -2420,11 +2751,14 @@
       <c r="E97" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F97" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>3532</v>
       </c>
@@ -2440,11 +2774,14 @@
       <c r="E98" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F98" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F98" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>3533</v>
       </c>
@@ -2460,11 +2797,14 @@
       <c r="E99" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F99" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F99" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>3541</v>
       </c>
@@ -2480,11 +2820,14 @@
       <c r="E100" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F100" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F100" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>3542</v>
       </c>
@@ -2500,11 +2843,14 @@
       <c r="E101" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F101" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F101" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>3543</v>
       </c>
@@ -2520,11 +2866,14 @@
       <c r="E102" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F102" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F102" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>3551</v>
       </c>
@@ -2540,11 +2889,14 @@
       <c r="E103" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F103" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>3552</v>
       </c>
@@ -2560,11 +2912,14 @@
       <c r="E104" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F104" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>3553</v>
       </c>
@@ -2580,11 +2935,14 @@
       <c r="E105" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F105" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F105" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>3561</v>
       </c>
@@ -2600,11 +2958,14 @@
       <c r="E106" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F106" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G106" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>3562</v>
       </c>
@@ -2620,11 +2981,14 @@
       <c r="E107" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F107" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>3563</v>
       </c>
@@ -2640,11 +3004,14 @@
       <c r="E108" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F108" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F108" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>3611</v>
       </c>
@@ -2660,11 +3027,14 @@
       <c r="E109" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F109" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F109" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G109" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>3612</v>
       </c>
@@ -2680,11 +3050,14 @@
       <c r="E110" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F110" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F110" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>3613</v>
       </c>
@@ -2700,11 +3073,14 @@
       <c r="E111" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F111" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F111" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>3621</v>
       </c>
@@ -2720,11 +3096,14 @@
       <c r="E112" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F112" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F112" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G112" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>3622</v>
       </c>
@@ -2740,11 +3119,14 @@
       <c r="E113" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F113" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F113" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>3623</v>
       </c>
@@ -2760,11 +3142,14 @@
       <c r="E114" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F114" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F114" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G114" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>3631</v>
       </c>
@@ -2780,11 +3165,14 @@
       <c r="E115" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F115" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F115" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G115" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>3632</v>
       </c>
@@ -2800,11 +3188,14 @@
       <c r="E116" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F116" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F116" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>3633</v>
       </c>
@@ -2820,11 +3211,14 @@
       <c r="E117" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F117" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F117" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>3641</v>
       </c>
@@ -2840,11 +3234,14 @@
       <c r="E118" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F118" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F118" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G118" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>3642</v>
       </c>
@@ -2860,11 +3257,14 @@
       <c r="E119" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F119" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G119" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>3643</v>
       </c>
@@ -2880,11 +3280,14 @@
       <c r="E120" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F120" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F120" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G120" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>3651</v>
       </c>
@@ -2900,11 +3303,14 @@
       <c r="E121" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F121" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F121" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G121" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>3652</v>
       </c>
@@ -2920,11 +3326,14 @@
       <c r="E122" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F122" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>3653</v>
       </c>
@@ -2940,11 +3349,14 @@
       <c r="E123" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F123" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F123" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>3661</v>
       </c>
@@ -2960,11 +3372,14 @@
       <c r="E124" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F124" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F124" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G124" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>3662</v>
       </c>
@@ -2980,11 +3395,14 @@
       <c r="E125" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F125" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>3663</v>
       </c>
@@ -3000,11 +3418,14 @@
       <c r="E126" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F126" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F126" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G126" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>3711</v>
       </c>
@@ -3020,11 +3441,14 @@
       <c r="E127" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F127" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G127" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>3712</v>
       </c>
@@ -3040,11 +3464,14 @@
       <c r="E128" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F128" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F128" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>3713</v>
       </c>
@@ -3060,11 +3487,14 @@
       <c r="E129" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F129" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F129" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>3721</v>
       </c>
@@ -3080,11 +3510,14 @@
       <c r="E130" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F130" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F130" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G130" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>3722</v>
       </c>
@@ -3100,11 +3533,14 @@
       <c r="E131" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F131" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>3723</v>
       </c>
@@ -3120,11 +3556,14 @@
       <c r="E132" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F132" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F132" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>3731</v>
       </c>
@@ -3140,11 +3579,14 @@
       <c r="E133" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F133" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F133" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G133" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>3732</v>
       </c>
@@ -3160,11 +3602,14 @@
       <c r="E134" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F134" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F134" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G134" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>3733</v>
       </c>
@@ -3180,11 +3625,14 @@
       <c r="E135" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F135" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F135" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G135" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>3741</v>
       </c>
@@ -3200,11 +3648,14 @@
       <c r="E136" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F136" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F136" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G136" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>3742</v>
       </c>
@@ -3220,11 +3671,14 @@
       <c r="E137" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F137" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F137" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>3743</v>
       </c>
@@ -3240,11 +3694,14 @@
       <c r="E138" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F138" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F138" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G138" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>3751</v>
       </c>
@@ -3260,11 +3717,14 @@
       <c r="E139" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F139" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F139" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G139" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>3752</v>
       </c>
@@ -3280,11 +3740,14 @@
       <c r="E140" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F140" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F140" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>3753</v>
       </c>
@@ -3300,11 +3763,14 @@
       <c r="E141" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F141" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F141" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G141" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>3761</v>
       </c>
@@ -3320,11 +3786,14 @@
       <c r="E142" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F142" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F142" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G142" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>3762</v>
       </c>
@@ -3340,11 +3809,14 @@
       <c r="E143" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F143" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F143" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>3763</v>
       </c>
@@ -3360,11 +3832,14 @@
       <c r="E144" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F144" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F144" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G144" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>5001</v>
       </c>
@@ -3380,11 +3855,14 @@
       <c r="E145" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F145" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F145" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>5002</v>
       </c>
@@ -3400,11 +3878,14 @@
       <c r="E146" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F146" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F146" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
         <v>6001</v>
       </c>
@@ -3420,11 +3901,14 @@
       <c r="E147" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F147" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F147" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
         <v>6002</v>
       </c>
@@ -3440,11 +3924,14 @@
       <c r="E148" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F148" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F148" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
         <v>6003</v>
       </c>
@@ -3460,11 +3947,14 @@
       <c r="E149" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F149" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F149" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
         <v>6004</v>
       </c>
@@ -3480,9 +3970,600 @@
       <c r="E150" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F150" s="6">
-        <v>0</v>
-      </c>
+      <c r="F150" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="7">
+        <v>7101</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D151" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G151" s="7"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="7">
+        <v>7102</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D152" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152" s="7"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="7">
+        <v>7103</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D153" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G153" s="7"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="7">
+        <v>7104</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D154" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G154" s="7"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="7">
+        <v>7201</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D155" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G155" s="7"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="7">
+        <v>7202</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D156" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="7"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="7">
+        <v>7203</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D157" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G157" s="7"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="7">
+        <v>7204</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D158" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G158" s="7"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="7">
+        <v>7301</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D159" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G159" s="7"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="7">
+        <v>7302</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D160" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G160" s="7"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="7">
+        <v>7303</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D161" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G161" s="7"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="7">
+        <v>7304</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D162" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G162" s="7"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="7">
+        <v>7401</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D163" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G163" s="7"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="7">
+        <v>7402</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D164" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="7"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="7">
+        <v>7403</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D165" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G165" s="7"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="7">
+        <v>7404</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D166" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G166" s="7"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="7">
+        <v>7501</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D167" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G167" s="7"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="7">
+        <v>7502</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D168" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="7"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="7">
+        <v>7503</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D169" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G169" s="7"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="7">
+        <v>7504</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D170" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G170" s="7"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="7">
+        <v>7601</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D171" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G171" s="7"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="7">
+        <v>7602</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D172" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="7"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="7">
+        <v>7603</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D173" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G173" s="7"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="7">
+        <v>7604</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D174" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G174" s="7"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="7">
+        <v>7701</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D175" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G175" s="7"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="7">
+        <v>7702</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D176" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="7"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="7">
+        <v>7703</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D177" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G177" s="7"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="7">
+        <v>7704</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D178" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G178" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD2415C-F57F-415B-82DA-A2BAA9B24BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76341D9-4C0B-4946-A73C-50D5972938B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20820" yWindow="1275" windowWidth="12675" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="27">
   <si>
     <t>ItemId</t>
   </si>
@@ -114,6 +114,10 @@
   <si>
     <t>Weapon</t>
   </si>
+  <si>
+    <t>Lantern</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -142,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -179,6 +183,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -207,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -218,6 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -520,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="9" style="2"/>
@@ -713,7 +724,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>1999</v>
+        <v>1008</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -735,54 +746,54 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>2001</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="A10" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>2002</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="A11" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
@@ -805,7 +816,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -828,7 +839,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
@@ -851,7 +862,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>8</v>
@@ -874,7 +885,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
@@ -897,7 +908,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
@@ -920,7 +931,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
@@ -942,54 +953,54 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>3111</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="A19" s="3">
+        <v>2008</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
-        <v>3112</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="A20" s="3">
+        <v>2009</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>10</v>
@@ -1004,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G21" s="4">
         <v>0</v>
@@ -1012,7 +1023,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
-        <v>3121</v>
+        <v>3112</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -1027,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
@@ -1035,7 +1046,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>3122</v>
+        <v>3113</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>10</v>
@@ -1050,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="4">
         <v>0</v>
@@ -1058,7 +1069,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>10</v>
@@ -1073,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
@@ -1081,7 +1092,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>3131</v>
+        <v>3122</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>10</v>
@@ -1096,7 +1107,7 @@
         <v>7</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -1104,7 +1115,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>3132</v>
+        <v>3123</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>10</v>
@@ -1119,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
@@ -1127,7 +1138,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>10</v>
@@ -1142,7 +1153,7 @@
         <v>7</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
@@ -1150,7 +1161,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>3141</v>
+        <v>3132</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>10</v>
@@ -1165,7 +1176,7 @@
         <v>7</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G28" s="4">
         <v>0</v>
@@ -1173,7 +1184,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>3142</v>
+        <v>3133</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>10</v>
@@ -1188,7 +1199,7 @@
         <v>7</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29" s="4">
         <v>0</v>
@@ -1196,7 +1207,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>10</v>
@@ -1211,7 +1222,7 @@
         <v>7</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="4">
         <v>0</v>
@@ -1219,7 +1230,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>3151</v>
+        <v>3142</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>10</v>
@@ -1234,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31" s="4">
         <v>0</v>
@@ -1242,7 +1253,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>3152</v>
+        <v>3143</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>10</v>
@@ -1257,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -1265,7 +1276,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>10</v>
@@ -1280,7 +1291,7 @@
         <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G33" s="4">
         <v>0</v>
@@ -1288,7 +1299,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>3161</v>
+        <v>3152</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>10</v>
@@ -1303,7 +1314,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" s="4">
         <v>0</v>
@@ -1311,7 +1322,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>3162</v>
+        <v>3153</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>10</v>
@@ -1326,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G35" s="4">
         <v>0</v>
@@ -1334,7 +1345,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>10</v>
@@ -1349,7 +1360,7 @@
         <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G36" s="4">
         <v>0</v>
@@ -1357,7 +1368,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>3211</v>
+        <v>3162</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>10</v>
@@ -1369,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G37" s="4">
         <v>0</v>
@@ -1380,7 +1391,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>3212</v>
+        <v>3163</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>10</v>
@@ -1392,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G38" s="4">
         <v>0</v>
@@ -1403,7 +1414,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>10</v>
@@ -1418,7 +1429,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G39" s="4">
         <v>0</v>
@@ -1426,7 +1437,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>3221</v>
+        <v>3212</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>10</v>
@@ -1441,7 +1452,7 @@
         <v>12</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G40" s="4">
         <v>0</v>
@@ -1449,7 +1460,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>3222</v>
+        <v>3213</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>10</v>
@@ -1464,7 +1475,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G41" s="4">
         <v>0</v>
@@ -1472,7 +1483,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>3223</v>
+        <v>3221</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>10</v>
@@ -1487,7 +1498,7 @@
         <v>12</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G42" s="4">
         <v>0</v>
@@ -1495,7 +1506,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>3231</v>
+        <v>3222</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>10</v>
@@ -1510,7 +1521,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G43" s="4">
         <v>0</v>
@@ -1518,7 +1529,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>3232</v>
+        <v>3223</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>10</v>
@@ -1533,7 +1544,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G44" s="4">
         <v>0</v>
@@ -1541,7 +1552,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>10</v>
@@ -1556,7 +1567,7 @@
         <v>12</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G45" s="4">
         <v>0</v>
@@ -1564,7 +1575,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>3241</v>
+        <v>3232</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>10</v>
@@ -1579,7 +1590,7 @@
         <v>12</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G46" s="4">
         <v>0</v>
@@ -1587,7 +1598,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>3242</v>
+        <v>3233</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>10</v>
@@ -1602,7 +1613,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G47" s="4">
         <v>0</v>
@@ -1610,7 +1621,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>10</v>
@@ -1625,7 +1636,7 @@
         <v>12</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G48" s="4">
         <v>0</v>
@@ -1633,7 +1644,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>3251</v>
+        <v>3242</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>10</v>
@@ -1648,7 +1659,7 @@
         <v>12</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G49" s="4">
         <v>0</v>
@@ -1656,7 +1667,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>3252</v>
+        <v>3243</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>10</v>
@@ -1671,7 +1682,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G50" s="4">
         <v>0</v>
@@ -1679,7 +1690,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>10</v>
@@ -1694,7 +1705,7 @@
         <v>12</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G51" s="4">
         <v>0</v>
@@ -1702,7 +1713,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
-        <v>3261</v>
+        <v>3252</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>10</v>
@@ -1717,7 +1728,7 @@
         <v>12</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G52" s="4">
         <v>0</v>
@@ -1725,7 +1736,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
-        <v>3262</v>
+        <v>3253</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>10</v>
@@ -1740,7 +1751,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G53" s="4">
         <v>0</v>
@@ -1748,7 +1759,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>10</v>
@@ -1763,7 +1774,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G54" s="4">
         <v>0</v>
@@ -1771,7 +1782,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
-        <v>3311</v>
+        <v>3262</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>10</v>
@@ -1783,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G55" s="4">
         <v>0</v>
@@ -1794,7 +1805,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
-        <v>3312</v>
+        <v>3263</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>10</v>
@@ -1806,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G56" s="4">
         <v>0</v>
@@ -1817,7 +1828,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>10</v>
@@ -1832,7 +1843,7 @@
         <v>13</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G57" s="4">
         <v>0</v>
@@ -1840,7 +1851,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
-        <v>3321</v>
+        <v>3312</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>10</v>
@@ -1855,7 +1866,7 @@
         <v>13</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G58" s="4">
         <v>0</v>
@@ -1863,7 +1874,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
-        <v>3322</v>
+        <v>3313</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>10</v>
@@ -1878,7 +1889,7 @@
         <v>13</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G59" s="4">
         <v>0</v>
@@ -1886,7 +1897,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>10</v>
@@ -1901,7 +1912,7 @@
         <v>13</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G60" s="4">
         <v>0</v>
@@ -1909,7 +1920,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
-        <v>3331</v>
+        <v>3322</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>10</v>
@@ -1924,7 +1935,7 @@
         <v>13</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G61" s="4">
         <v>0</v>
@@ -1932,7 +1943,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
-        <v>3332</v>
+        <v>3323</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>10</v>
@@ -1947,7 +1958,7 @@
         <v>13</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G62" s="4">
         <v>0</v>
@@ -1955,7 +1966,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>10</v>
@@ -1970,7 +1981,7 @@
         <v>13</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G63" s="4">
         <v>0</v>
@@ -1978,7 +1989,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
-        <v>3341</v>
+        <v>3332</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>10</v>
@@ -1993,7 +2004,7 @@
         <v>13</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -2001,7 +2012,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
-        <v>3342</v>
+        <v>3333</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>10</v>
@@ -2016,7 +2027,7 @@
         <v>13</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -2024,7 +2035,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
-        <v>3343</v>
+        <v>3341</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>10</v>
@@ -2039,7 +2050,7 @@
         <v>13</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G66" s="4">
         <v>0</v>
@@ -2047,7 +2058,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
-        <v>3351</v>
+        <v>3342</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>10</v>
@@ -2062,7 +2073,7 @@
         <v>13</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G67" s="4">
         <v>0</v>
@@ -2070,7 +2081,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>10</v>
@@ -2085,7 +2096,7 @@
         <v>13</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G68" s="4">
         <v>0</v>
@@ -2093,7 +2104,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
-        <v>3353</v>
+        <v>3351</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>10</v>
@@ -2108,7 +2119,7 @@
         <v>13</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G69" s="4">
         <v>0</v>
@@ -2116,7 +2127,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
-        <v>3361</v>
+        <v>3352</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>10</v>
@@ -2131,7 +2142,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G70" s="4">
         <v>0</v>
@@ -2139,7 +2150,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
-        <v>3362</v>
+        <v>3353</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>10</v>
@@ -2154,7 +2165,7 @@
         <v>13</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -2162,7 +2173,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>10</v>
@@ -2177,7 +2188,7 @@
         <v>13</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G72" s="4">
         <v>0</v>
@@ -2185,7 +2196,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
-        <v>3411</v>
+        <v>3362</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>10</v>
@@ -2197,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G73" s="4">
         <v>0</v>
@@ -2208,7 +2219,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
-        <v>3412</v>
+        <v>3363</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>10</v>
@@ -2220,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G74" s="4">
         <v>0</v>
@@ -2231,7 +2242,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>10</v>
@@ -2246,7 +2257,7 @@
         <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G75" s="4">
         <v>0</v>
@@ -2254,7 +2265,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
-        <v>3421</v>
+        <v>3412</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>10</v>
@@ -2269,7 +2280,7 @@
         <v>9</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G76" s="4">
         <v>0</v>
@@ -2277,7 +2288,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
-        <v>3422</v>
+        <v>3413</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>10</v>
@@ -2292,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
@@ -2300,7 +2311,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
-        <v>3423</v>
+        <v>3421</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>10</v>
@@ -2315,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G78" s="4">
         <v>0</v>
@@ -2323,7 +2334,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
-        <v>3431</v>
+        <v>3422</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>10</v>
@@ -2338,7 +2349,7 @@
         <v>9</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G79" s="4">
         <v>0</v>
@@ -2346,7 +2357,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
-        <v>3432</v>
+        <v>3423</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>10</v>
@@ -2361,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G80" s="4">
         <v>0</v>
@@ -2369,7 +2380,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>10</v>
@@ -2384,7 +2395,7 @@
         <v>9</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G81" s="4">
         <v>0</v>
@@ -2392,7 +2403,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
-        <v>3441</v>
+        <v>3432</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>10</v>
@@ -2407,7 +2418,7 @@
         <v>9</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -2415,7 +2426,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
-        <v>3442</v>
+        <v>3433</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>10</v>
@@ -2430,7 +2441,7 @@
         <v>9</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
@@ -2438,7 +2449,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
-        <v>3443</v>
+        <v>3441</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>10</v>
@@ -2453,7 +2464,7 @@
         <v>9</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
@@ -2461,7 +2472,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
-        <v>3451</v>
+        <v>3442</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>10</v>
@@ -2476,7 +2487,7 @@
         <v>9</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
@@ -2484,7 +2495,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
-        <v>3452</v>
+        <v>3443</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>10</v>
@@ -2499,7 +2510,7 @@
         <v>9</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G86" s="4">
         <v>0</v>
@@ -2507,7 +2518,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
-        <v>3453</v>
+        <v>3451</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>10</v>
@@ -2522,7 +2533,7 @@
         <v>9</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G87" s="4">
         <v>0</v>
@@ -2530,7 +2541,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
-        <v>3461</v>
+        <v>3452</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>10</v>
@@ -2545,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G88" s="4">
         <v>0</v>
@@ -2553,7 +2564,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
-        <v>3462</v>
+        <v>3453</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>10</v>
@@ -2568,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -2576,7 +2587,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>10</v>
@@ -2591,7 +2602,7 @@
         <v>9</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G90" s="4">
         <v>0</v>
@@ -2599,7 +2610,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
-        <v>3511</v>
+        <v>3462</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>10</v>
@@ -2611,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G91" s="4">
         <v>0</v>
@@ -2622,7 +2633,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
-        <v>3512</v>
+        <v>3463</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>10</v>
@@ -2634,10 +2645,10 @@
         <v>0</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G92" s="4">
         <v>0</v>
@@ -2645,7 +2656,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>10</v>
@@ -2660,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G93" s="4">
         <v>0</v>
@@ -2668,7 +2679,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
-        <v>3521</v>
+        <v>3512</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>10</v>
@@ -2683,7 +2694,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G94" s="4">
         <v>0</v>
@@ -2691,7 +2702,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
-        <v>3522</v>
+        <v>3513</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>10</v>
@@ -2706,7 +2717,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G95" s="4">
         <v>0</v>
@@ -2714,7 +2725,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>10</v>
@@ -2729,7 +2740,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G96" s="4">
         <v>0</v>
@@ -2737,7 +2748,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
-        <v>3531</v>
+        <v>3522</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>10</v>
@@ -2752,7 +2763,7 @@
         <v>14</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G97" s="4">
         <v>0</v>
@@ -2760,7 +2771,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
-        <v>3532</v>
+        <v>3523</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>10</v>
@@ -2775,7 +2786,7 @@
         <v>14</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -2783,7 +2794,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>10</v>
@@ -2798,7 +2809,7 @@
         <v>14</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G99" s="4">
         <v>0</v>
@@ -2806,7 +2817,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
-        <v>3541</v>
+        <v>3532</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>10</v>
@@ -2821,7 +2832,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G100" s="4">
         <v>0</v>
@@ -2829,7 +2840,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
-        <v>3542</v>
+        <v>3533</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>10</v>
@@ -2844,7 +2855,7 @@
         <v>14</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G101" s="4">
         <v>0</v>
@@ -2852,7 +2863,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>10</v>
@@ -2867,7 +2878,7 @@
         <v>14</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G102" s="4">
         <v>0</v>
@@ -2875,7 +2886,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
-        <v>3551</v>
+        <v>3542</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>10</v>
@@ -2890,7 +2901,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G103" s="4">
         <v>0</v>
@@ -2898,7 +2909,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
-        <v>3552</v>
+        <v>3543</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>10</v>
@@ -2913,7 +2924,7 @@
         <v>14</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G104" s="4">
         <v>0</v>
@@ -2921,7 +2932,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
-        <v>3553</v>
+        <v>3551</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>10</v>
@@ -2936,7 +2947,7 @@
         <v>14</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G105" s="4">
         <v>0</v>
@@ -2944,7 +2955,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
-        <v>3561</v>
+        <v>3552</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>10</v>
@@ -2959,7 +2970,7 @@
         <v>14</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G106" s="4">
         <v>0</v>
@@ -2967,7 +2978,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
-        <v>3562</v>
+        <v>3553</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>10</v>
@@ -2982,7 +2993,7 @@
         <v>14</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G107" s="4">
         <v>0</v>
@@ -2990,7 +3001,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>10</v>
@@ -3005,7 +3016,7 @@
         <v>14</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G108" s="4">
         <v>0</v>
@@ -3013,7 +3024,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
-        <v>3611</v>
+        <v>3562</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>10</v>
@@ -3025,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G109" s="4">
         <v>0</v>
@@ -3036,7 +3047,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
-        <v>3612</v>
+        <v>3563</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>10</v>
@@ -3048,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G110" s="4">
         <v>0</v>
@@ -3059,7 +3070,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>10</v>
@@ -3074,7 +3085,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G111" s="4">
         <v>0</v>
@@ -3082,7 +3093,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
-        <v>3621</v>
+        <v>3612</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>10</v>
@@ -3097,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G112" s="4">
         <v>0</v>
@@ -3105,7 +3116,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
-        <v>3622</v>
+        <v>3613</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>10</v>
@@ -3120,7 +3131,7 @@
         <v>15</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G113" s="4">
         <v>0</v>
@@ -3128,7 +3139,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
-        <v>3623</v>
+        <v>3621</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>10</v>
@@ -3143,7 +3154,7 @@
         <v>15</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G114" s="4">
         <v>0</v>
@@ -3151,7 +3162,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
-        <v>3631</v>
+        <v>3622</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>10</v>
@@ -3166,7 +3177,7 @@
         <v>15</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G115" s="4">
         <v>0</v>
@@ -3174,7 +3185,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
-        <v>3632</v>
+        <v>3623</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>10</v>
@@ -3189,7 +3200,7 @@
         <v>15</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G116" s="4">
         <v>0</v>
@@ -3197,7 +3208,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
-        <v>3633</v>
+        <v>3631</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>10</v>
@@ -3212,7 +3223,7 @@
         <v>15</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G117" s="4">
         <v>0</v>
@@ -3220,7 +3231,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
-        <v>3641</v>
+        <v>3632</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>10</v>
@@ -3235,7 +3246,7 @@
         <v>15</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G118" s="4">
         <v>0</v>
@@ -3243,7 +3254,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
-        <v>3642</v>
+        <v>3633</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>10</v>
@@ -3258,7 +3269,7 @@
         <v>15</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G119" s="4">
         <v>0</v>
@@ -3266,7 +3277,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>10</v>
@@ -3281,7 +3292,7 @@
         <v>15</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G120" s="4">
         <v>0</v>
@@ -3289,7 +3300,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>10</v>
@@ -3304,7 +3315,7 @@
         <v>15</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G121" s="4">
         <v>0</v>
@@ -3312,7 +3323,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
-        <v>3652</v>
+        <v>3643</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>10</v>
@@ -3327,7 +3338,7 @@
         <v>15</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G122" s="4">
         <v>0</v>
@@ -3335,7 +3346,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
-        <v>3653</v>
+        <v>3651</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>10</v>
@@ -3350,7 +3361,7 @@
         <v>15</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G123" s="4">
         <v>0</v>
@@ -3358,7 +3369,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
-        <v>3661</v>
+        <v>3652</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>10</v>
@@ -3373,7 +3384,7 @@
         <v>15</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G124" s="4">
         <v>0</v>
@@ -3381,7 +3392,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
-        <v>3662</v>
+        <v>3653</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>10</v>
@@ -3396,7 +3407,7 @@
         <v>15</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G125" s="4">
         <v>0</v>
@@ -3404,7 +3415,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
-        <v>3663</v>
+        <v>3661</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>10</v>
@@ -3419,7 +3430,7 @@
         <v>15</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G126" s="4">
         <v>0</v>
@@ -3427,7 +3438,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
-        <v>3711</v>
+        <v>3662</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>10</v>
@@ -3439,10 +3450,10 @@
         <v>0</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
@@ -3450,7 +3461,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
-        <v>3712</v>
+        <v>3663</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>10</v>
@@ -3462,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G128" s="4">
         <v>0</v>
@@ -3473,7 +3484,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
-        <v>3713</v>
+        <v>3711</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>10</v>
@@ -3488,7 +3499,7 @@
         <v>16</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G129" s="4">
         <v>0</v>
@@ -3496,7 +3507,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
-        <v>3721</v>
+        <v>3712</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>10</v>
@@ -3511,7 +3522,7 @@
         <v>16</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -3519,7 +3530,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
-        <v>3722</v>
+        <v>3713</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>10</v>
@@ -3534,7 +3545,7 @@
         <v>16</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -3542,7 +3553,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
-        <v>3723</v>
+        <v>3721</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>10</v>
@@ -3557,7 +3568,7 @@
         <v>16</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G132" s="4">
         <v>0</v>
@@ -3565,7 +3576,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
-        <v>3731</v>
+        <v>3722</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>10</v>
@@ -3580,7 +3591,7 @@
         <v>16</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G133" s="4">
         <v>0</v>
@@ -3588,7 +3599,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
-        <v>3732</v>
+        <v>3723</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>10</v>
@@ -3603,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G134" s="4">
         <v>0</v>
@@ -3611,7 +3622,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
-        <v>3733</v>
+        <v>3731</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>10</v>
@@ -3626,7 +3637,7 @@
         <v>16</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G135" s="4">
         <v>0</v>
@@ -3634,7 +3645,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
-        <v>3741</v>
+        <v>3732</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>10</v>
@@ -3649,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G136" s="4">
         <v>0</v>
@@ -3657,7 +3668,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
-        <v>3742</v>
+        <v>3733</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>10</v>
@@ -3672,7 +3683,7 @@
         <v>16</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G137" s="4">
         <v>0</v>
@@ -3680,7 +3691,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>10</v>
@@ -3695,7 +3706,7 @@
         <v>16</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G138" s="4">
         <v>0</v>
@@ -3703,7 +3714,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
-        <v>3751</v>
+        <v>3742</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>10</v>
@@ -3718,7 +3729,7 @@
         <v>16</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G139" s="4">
         <v>0</v>
@@ -3726,7 +3737,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
-        <v>3752</v>
+        <v>3743</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>10</v>
@@ -3741,7 +3752,7 @@
         <v>16</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G140" s="4">
         <v>0</v>
@@ -3749,7 +3760,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>10</v>
@@ -3764,7 +3775,7 @@
         <v>16</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G141" s="4">
         <v>0</v>
@@ -3772,7 +3783,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
-        <v>3761</v>
+        <v>3752</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>10</v>
@@ -3787,7 +3798,7 @@
         <v>16</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G142" s="4">
         <v>0</v>
@@ -3795,7 +3806,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
-        <v>3762</v>
+        <v>3753</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>10</v>
@@ -3810,7 +3821,7 @@
         <v>16</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G143" s="4">
         <v>0</v>
@@ -3818,7 +3829,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
-        <v>3763</v>
+        <v>3761</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>10</v>
@@ -3833,107 +3844,107 @@
         <v>16</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G144" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="5">
+      <c r="A145" s="4">
+        <v>3762</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="4">
+        <v>3763</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G146" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="5">
         <v>5001</v>
       </c>
-      <c r="B145" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C145" s="5" t="s">
+      <c r="B147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D145" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E145" s="5" t="s">
+      <c r="D147" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E147" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F147" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G145" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="5">
+      <c r="G147" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="5">
         <v>5002</v>
       </c>
-      <c r="B146" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C146" s="5" t="s">
+      <c r="B148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D146" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E146" s="5" t="s">
+      <c r="D148" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E148" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F148" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G146" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="6">
-        <v>6001</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D147" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G147" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="6">
-        <v>6002</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D148" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G148" s="6">
+      <c r="G148" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>10</v>
@@ -3956,7 +3967,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>10</v>
@@ -3978,50 +3989,54 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="7">
-        <v>7101</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D151" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G151" s="7"/>
+      <c r="A151" s="6">
+        <v>6003</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="7">
-        <v>7102</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C152" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D152" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G152" s="7"/>
+      <c r="A152" s="6">
+        <v>6004</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
-        <v>7103</v>
+        <v>7101</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>25</v>
@@ -4036,13 +4051,13 @@
         <v>7</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G153" s="7"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="7">
-        <v>7104</v>
+        <v>7102</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>25</v>
@@ -4057,13 +4072,13 @@
         <v>7</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G154" s="7"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
-        <v>7201</v>
+        <v>7103</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>25</v>
@@ -4075,16 +4090,16 @@
         <v>1</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G155" s="7"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
-        <v>7202</v>
+        <v>7104</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>25</v>
@@ -4096,16 +4111,16 @@
         <v>1</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G156" s="7"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="7">
-        <v>7203</v>
+        <v>7201</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>25</v>
@@ -4120,13 +4135,13 @@
         <v>12</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G157" s="7"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
-        <v>7204</v>
+        <v>7202</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>25</v>
@@ -4141,13 +4156,13 @@
         <v>12</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G158" s="7"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
-        <v>7301</v>
+        <v>7203</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>25</v>
@@ -4159,16 +4174,16 @@
         <v>1</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G159" s="7"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
-        <v>7302</v>
+        <v>7204</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>25</v>
@@ -4180,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G160" s="7"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="7">
-        <v>7303</v>
+        <v>7301</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>25</v>
@@ -4204,13 +4219,13 @@
         <v>13</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G161" s="7"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="7">
-        <v>7304</v>
+        <v>7302</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>25</v>
@@ -4225,13 +4240,13 @@
         <v>13</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G162" s="7"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
-        <v>7401</v>
+        <v>7303</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>25</v>
@@ -4243,16 +4258,16 @@
         <v>1</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G163" s="7"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
-        <v>7402</v>
+        <v>7304</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>25</v>
@@ -4264,16 +4279,16 @@
         <v>1</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G164" s="7"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
-        <v>7403</v>
+        <v>7401</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>25</v>
@@ -4288,13 +4303,13 @@
         <v>9</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G165" s="7"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="7">
-        <v>7404</v>
+        <v>7402</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>25</v>
@@ -4309,13 +4324,13 @@
         <v>9</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G166" s="7"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="7">
-        <v>7501</v>
+        <v>7403</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>25</v>
@@ -4327,16 +4342,16 @@
         <v>1</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G167" s="7"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
-        <v>7502</v>
+        <v>7404</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>25</v>
@@ -4348,16 +4363,16 @@
         <v>1</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G168" s="7"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
-        <v>7503</v>
+        <v>7501</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>25</v>
@@ -4372,13 +4387,13 @@
         <v>14</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G169" s="7"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="7">
-        <v>7504</v>
+        <v>7502</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>25</v>
@@ -4393,13 +4408,13 @@
         <v>14</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G170" s="7"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="7">
-        <v>7601</v>
+        <v>7503</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>25</v>
@@ -4411,16 +4426,16 @@
         <v>1</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G171" s="7"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
-        <v>7602</v>
+        <v>7504</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>25</v>
@@ -4432,16 +4447,16 @@
         <v>1</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G172" s="7"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
-        <v>7603</v>
+        <v>7601</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>25</v>
@@ -4456,13 +4471,13 @@
         <v>15</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G173" s="7"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="7">
-        <v>7604</v>
+        <v>7602</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>25</v>
@@ -4477,13 +4492,13 @@
         <v>15</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G174" s="7"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="7">
-        <v>7701</v>
+        <v>7603</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>25</v>
@@ -4495,16 +4510,16 @@
         <v>1</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G175" s="7"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="7">
-        <v>7702</v>
+        <v>7604</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>25</v>
@@ -4516,16 +4531,16 @@
         <v>1</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G176" s="7"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="7">
-        <v>7703</v>
+        <v>7701</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>25</v>
@@ -4540,13 +4555,13 @@
         <v>16</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G177" s="7"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="7">
-        <v>7704</v>
+        <v>7702</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>25</v>
@@ -4561,9 +4576,639 @@
         <v>16</v>
       </c>
       <c r="F178" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" s="7"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="7">
+        <v>7703</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D179" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G179" s="7"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="7">
+        <v>7704</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D180" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G178" s="7"/>
+      <c r="G180" s="7"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="8">
+        <v>8101</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D181" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G181" s="8"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="8">
+        <v>8102</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D182" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182" s="8"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="8">
+        <v>8103</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D183" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G183" s="8"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="8">
+        <v>8104</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D184" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G184" s="8"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="8">
+        <v>8201</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D185" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G185" s="8"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="8">
+        <v>8202</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D186" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G186" s="8"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="8">
+        <v>8203</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D187" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G187" s="8"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="8">
+        <v>8204</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D188" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G188" s="8"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="8">
+        <v>8301</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D189" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G189" s="8"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="8">
+        <v>8302</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D190" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G190" s="8"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="8">
+        <v>8303</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D191" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G191" s="8"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="8">
+        <v>8304</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D192" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G192" s="8"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="8">
+        <v>8401</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D193" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G193" s="8"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="8">
+        <v>8402</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D194" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G194" s="8"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="8">
+        <v>8403</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D195" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G195" s="8"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="8">
+        <v>8404</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D196" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G196" s="8"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="8">
+        <v>8501</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D197" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G197" s="8"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="8">
+        <v>8502</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D198" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G198" s="8"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="8">
+        <v>8503</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D199" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G199" s="8"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="8">
+        <v>8504</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D200" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G200" s="8"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="8">
+        <v>8601</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D201" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G201" s="8"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="8">
+        <v>8602</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C202" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D202" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G202" s="8"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="8">
+        <v>8603</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D203" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E203" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G203" s="8"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="8">
+        <v>8604</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D204" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E204" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G204" s="8"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="8">
+        <v>8701</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D205" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G205" s="8"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" s="8">
+        <v>8702</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D206" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G206" s="8"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" s="8">
+        <v>8703</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C207" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D207" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E207" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G207" s="8"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" s="8">
+        <v>8704</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D208" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E208" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G208" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76341D9-4C0B-4946-A73C-50D5972938B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D030B0-10DD-4E25-BB39-D3B8E7BAD5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40815" yWindow="1635" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="28">
   <si>
     <t>ItemId</t>
   </si>
@@ -116,6 +116,10 @@
   </si>
   <si>
     <t>Lantern</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1003,7 +1007,7 @@
         <v>3111</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>11</v>
@@ -1026,7 +1030,7 @@
         <v>3112</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
@@ -1049,7 +1053,7 @@
         <v>3113</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>11</v>
@@ -1072,7 +1076,7 @@
         <v>3121</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>11</v>
@@ -1095,7 +1099,7 @@
         <v>3122</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>11</v>
@@ -1118,7 +1122,7 @@
         <v>3123</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>11</v>
@@ -1141,7 +1145,7 @@
         <v>3131</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>11</v>
@@ -1164,7 +1168,7 @@
         <v>3132</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>11</v>
@@ -1187,7 +1191,7 @@
         <v>3133</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>11</v>
@@ -1210,7 +1214,7 @@
         <v>3141</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>11</v>
@@ -1233,7 +1237,7 @@
         <v>3142</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>11</v>
@@ -1256,7 +1260,7 @@
         <v>3143</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>11</v>
@@ -1279,7 +1283,7 @@
         <v>3151</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>11</v>
@@ -1302,7 +1306,7 @@
         <v>3152</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>11</v>
@@ -1325,7 +1329,7 @@
         <v>3153</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>11</v>
@@ -1348,7 +1352,7 @@
         <v>3161</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>11</v>
@@ -1371,7 +1375,7 @@
         <v>3162</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>11</v>
@@ -1394,7 +1398,7 @@
         <v>3163</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>11</v>
@@ -1417,7 +1421,7 @@
         <v>3211</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>11</v>
@@ -1440,7 +1444,7 @@
         <v>3212</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>11</v>
@@ -1463,7 +1467,7 @@
         <v>3213</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>11</v>
@@ -1486,7 +1490,7 @@
         <v>3221</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>11</v>
@@ -1509,7 +1513,7 @@
         <v>3222</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>11</v>
@@ -1532,7 +1536,7 @@
         <v>3223</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>11</v>
@@ -1555,7 +1559,7 @@
         <v>3231</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>11</v>
@@ -1578,7 +1582,7 @@
         <v>3232</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>11</v>
@@ -1601,7 +1605,7 @@
         <v>3233</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>11</v>
@@ -1624,7 +1628,7 @@
         <v>3241</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>11</v>
@@ -1647,7 +1651,7 @@
         <v>3242</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>11</v>
@@ -1670,7 +1674,7 @@
         <v>3243</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>11</v>
@@ -1693,7 +1697,7 @@
         <v>3251</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>11</v>
@@ -1716,7 +1720,7 @@
         <v>3252</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>11</v>
@@ -1739,7 +1743,7 @@
         <v>3253</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>11</v>
@@ -1762,7 +1766,7 @@
         <v>3261</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>11</v>
@@ -1785,7 +1789,7 @@
         <v>3262</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>11</v>
@@ -1808,7 +1812,7 @@
         <v>3263</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>11</v>
@@ -1831,7 +1835,7 @@
         <v>3311</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>11</v>
@@ -1854,7 +1858,7 @@
         <v>3312</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>11</v>
@@ -1877,7 +1881,7 @@
         <v>3313</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>11</v>
@@ -1900,7 +1904,7 @@
         <v>3321</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>11</v>
@@ -1923,7 +1927,7 @@
         <v>3322</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>11</v>
@@ -1946,7 +1950,7 @@
         <v>3323</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>11</v>
@@ -1969,7 +1973,7 @@
         <v>3331</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>11</v>
@@ -1992,7 +1996,7 @@
         <v>3332</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>11</v>
@@ -2015,7 +2019,7 @@
         <v>3333</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>11</v>
@@ -2038,7 +2042,7 @@
         <v>3341</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>11</v>
@@ -2061,7 +2065,7 @@
         <v>3342</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>11</v>
@@ -2084,7 +2088,7 @@
         <v>3343</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>11</v>
@@ -2107,7 +2111,7 @@
         <v>3351</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>11</v>
@@ -2130,7 +2134,7 @@
         <v>3352</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>11</v>
@@ -2153,7 +2157,7 @@
         <v>3353</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>11</v>
@@ -2176,7 +2180,7 @@
         <v>3361</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>11</v>
@@ -2199,7 +2203,7 @@
         <v>3362</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>11</v>
@@ -2222,7 +2226,7 @@
         <v>3363</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>11</v>
@@ -2245,7 +2249,7 @@
         <v>3411</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>11</v>
@@ -2268,7 +2272,7 @@
         <v>3412</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>11</v>
@@ -2291,7 +2295,7 @@
         <v>3413</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>11</v>
@@ -2314,7 +2318,7 @@
         <v>3421</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>11</v>
@@ -2337,7 +2341,7 @@
         <v>3422</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>11</v>
@@ -2360,7 +2364,7 @@
         <v>3423</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>11</v>
@@ -2383,7 +2387,7 @@
         <v>3431</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>11</v>
@@ -2406,7 +2410,7 @@
         <v>3432</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>11</v>
@@ -2429,7 +2433,7 @@
         <v>3433</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>11</v>
@@ -2452,7 +2456,7 @@
         <v>3441</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>11</v>
@@ -2475,7 +2479,7 @@
         <v>3442</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>11</v>
@@ -2498,7 +2502,7 @@
         <v>3443</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>11</v>
@@ -2521,7 +2525,7 @@
         <v>3451</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>11</v>
@@ -2544,7 +2548,7 @@
         <v>3452</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>11</v>
@@ -2567,7 +2571,7 @@
         <v>3453</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>11</v>
@@ -2590,7 +2594,7 @@
         <v>3461</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>11</v>
@@ -2613,7 +2617,7 @@
         <v>3462</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>11</v>
@@ -2636,7 +2640,7 @@
         <v>3463</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>11</v>
@@ -2659,7 +2663,7 @@
         <v>3511</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>11</v>
@@ -2682,7 +2686,7 @@
         <v>3512</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>11</v>
@@ -2705,7 +2709,7 @@
         <v>3513</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>11</v>
@@ -2728,7 +2732,7 @@
         <v>3521</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>11</v>
@@ -2751,7 +2755,7 @@
         <v>3522</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>11</v>
@@ -2774,7 +2778,7 @@
         <v>3523</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>11</v>
@@ -2797,7 +2801,7 @@
         <v>3531</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>11</v>
@@ -2820,7 +2824,7 @@
         <v>3532</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>11</v>
@@ -2843,7 +2847,7 @@
         <v>3533</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>11</v>
@@ -2866,7 +2870,7 @@
         <v>3541</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>11</v>
@@ -2889,7 +2893,7 @@
         <v>3542</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>11</v>
@@ -2912,7 +2916,7 @@
         <v>3543</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>11</v>
@@ -2935,7 +2939,7 @@
         <v>3551</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>11</v>
@@ -2958,7 +2962,7 @@
         <v>3552</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>11</v>
@@ -2981,7 +2985,7 @@
         <v>3553</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>11</v>
@@ -3004,7 +3008,7 @@
         <v>3561</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>11</v>
@@ -3027,7 +3031,7 @@
         <v>3562</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>11</v>
@@ -3050,7 +3054,7 @@
         <v>3563</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>11</v>
@@ -3073,7 +3077,7 @@
         <v>3611</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>11</v>
@@ -3096,7 +3100,7 @@
         <v>3612</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>11</v>
@@ -3119,7 +3123,7 @@
         <v>3613</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>11</v>
@@ -3142,7 +3146,7 @@
         <v>3621</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>11</v>
@@ -3165,7 +3169,7 @@
         <v>3622</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>11</v>
@@ -3188,7 +3192,7 @@
         <v>3623</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>11</v>
@@ -3211,7 +3215,7 @@
         <v>3631</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>11</v>
@@ -3234,7 +3238,7 @@
         <v>3632</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>11</v>
@@ -3257,7 +3261,7 @@
         <v>3633</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>11</v>
@@ -3280,7 +3284,7 @@
         <v>3641</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>11</v>
@@ -3303,7 +3307,7 @@
         <v>3642</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>11</v>
@@ -3326,7 +3330,7 @@
         <v>3643</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>11</v>
@@ -3349,7 +3353,7 @@
         <v>3651</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>11</v>
@@ -3372,7 +3376,7 @@
         <v>3652</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>11</v>
@@ -3395,7 +3399,7 @@
         <v>3653</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>11</v>
@@ -3418,7 +3422,7 @@
         <v>3661</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>11</v>
@@ -3441,7 +3445,7 @@
         <v>3662</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>11</v>
@@ -3464,7 +3468,7 @@
         <v>3663</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>11</v>
@@ -3487,7 +3491,7 @@
         <v>3711</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>11</v>
@@ -3510,7 +3514,7 @@
         <v>3712</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>11</v>
@@ -3533,7 +3537,7 @@
         <v>3713</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>11</v>
@@ -3556,7 +3560,7 @@
         <v>3721</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>11</v>
@@ -3579,7 +3583,7 @@
         <v>3722</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>11</v>
@@ -3602,7 +3606,7 @@
         <v>3723</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>11</v>
@@ -3625,7 +3629,7 @@
         <v>3731</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>11</v>
@@ -3648,7 +3652,7 @@
         <v>3732</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>11</v>
@@ -3671,7 +3675,7 @@
         <v>3733</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>11</v>
@@ -3694,7 +3698,7 @@
         <v>3741</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>11</v>
@@ -3717,7 +3721,7 @@
         <v>3742</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>11</v>
@@ -3740,7 +3744,7 @@
         <v>3743</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>11</v>
@@ -3763,7 +3767,7 @@
         <v>3751</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>11</v>
@@ -3786,7 +3790,7 @@
         <v>3752</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>11</v>
@@ -3809,7 +3813,7 @@
         <v>3753</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>11</v>
@@ -3832,7 +3836,7 @@
         <v>3761</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>11</v>
@@ -3855,7 +3859,7 @@
         <v>3762</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>11</v>
@@ -3878,7 +3882,7 @@
         <v>3763</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>11</v>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FED143-0FD4-4669-868E-3080BB7E54C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E778FD-84AE-48E9-BE80-41D22881EC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7185" yWindow="1200" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="32">
   <si>
     <t>ItemId</t>
   </si>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="9" style="2"/>
@@ -791,7 +791,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1999</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -813,123 +813,123 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>2001</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="A12" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>2002</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="A13" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>2003</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="A14" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>2004</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="A15" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>2005</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="A16" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
@@ -952,7 +952,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>8</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -1020,123 +1020,123 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>3111</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="A21" s="3">
+        <v>2005</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>3121</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="4">
-        <v>1</v>
+      <c r="A22" s="3">
+        <v>2006</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>3131</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="4">
-        <v>2</v>
+      <c r="A23" s="3">
+        <v>2007</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>3141</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="4">
-        <v>3</v>
+      <c r="A24" s="3">
+        <v>2008</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>3151</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="4">
-        <v>4</v>
+      <c r="A25" s="3">
+        <v>2009</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>3161</v>
+        <v>3111</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>27</v>
@@ -1154,12 +1154,12 @@
         <v>20</v>
       </c>
       <c r="G26" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>3211</v>
+        <v>3121</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>27</v>
@@ -1171,21 +1171,21 @@
         <v>0</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>3221</v>
+        <v>3131</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>11</v>
@@ -1194,21 +1194,21 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>3231</v>
+        <v>3141</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>11</v>
@@ -1217,21 +1217,21 @@
         <v>0</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>3241</v>
+        <v>3151</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>11</v>
@@ -1240,21 +1240,21 @@
         <v>0</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>3251</v>
+        <v>3161</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>11</v>
@@ -1263,21 +1263,21 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>3261</v>
+        <v>3211</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>11</v>
@@ -1292,12 +1292,12 @@
         <v>20</v>
       </c>
       <c r="G32" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>3311</v>
+        <v>3221</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>28</v>
@@ -1309,18 +1309,18 @@
         <v>0</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>3321</v>
+        <v>3231</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>28</v>
@@ -1332,18 +1332,18 @@
         <v>0</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G34" s="4">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>3331</v>
+        <v>3241</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>28</v>
@@ -1355,18 +1355,18 @@
         <v>0</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G35" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>3341</v>
+        <v>3251</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>28</v>
@@ -1378,18 +1378,18 @@
         <v>0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G36" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>3351</v>
+        <v>3261</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>28</v>
@@ -1401,18 +1401,18 @@
         <v>0</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G37" s="4">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>3361</v>
+        <v>3311</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>28</v>
@@ -1430,255 +1430,265 @@
         <v>20</v>
       </c>
       <c r="G38" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>3321</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>3331</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>3341</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>3351</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>3361</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
         <v>5001</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="s">
+      <c r="D44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="F44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>5002</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="D45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
+      <c r="F45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
         <v>6001</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B46" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D46" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="6">
+      <c r="F46" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="6">
         <v>6002</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B47" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="D47" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="6">
+      <c r="F47" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
         <v>6003</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B48" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="D48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="6">
+      <c r="F48" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
         <v>6004</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B49" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C49" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="D49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
-        <v>7101</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D45" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
-        <v>7102</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
-        <v>7103</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="7"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
-        <v>7104</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="7"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
-        <v>7201</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="7"/>
+      <c r="F49" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
-        <v>7202</v>
+        <v>7101</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>25</v>
@@ -1690,16 +1700,16 @@
         <v>1</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
-        <v>7203</v>
+        <v>7102</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>25</v>
@@ -1711,16 +1721,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
-        <v>7204</v>
+        <v>7103</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>25</v>
@@ -1732,16 +1742,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G52" s="7"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
-        <v>7301</v>
+        <v>7104</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>25</v>
@@ -1753,16 +1763,16 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
-        <v>7302</v>
+        <v>7201</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>25</v>
@@ -1774,16 +1784,16 @@
         <v>1</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G54" s="7"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
-        <v>7303</v>
+        <v>7202</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>25</v>
@@ -1795,16 +1805,16 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
-        <v>7304</v>
+        <v>7203</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>25</v>
@@ -1816,16 +1826,16 @@
         <v>1</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G56" s="7"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>7401</v>
+        <v>7204</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>25</v>
@@ -1837,16 +1847,16 @@
         <v>1</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G57" s="7"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
-        <v>7402</v>
+        <v>7301</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>25</v>
@@ -1858,16 +1868,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G58" s="7"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
-        <v>7403</v>
+        <v>7302</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>25</v>
@@ -1879,16 +1889,16 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G59" s="7"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
-        <v>7404</v>
+        <v>7303</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>25</v>
@@ -1900,16 +1910,16 @@
         <v>1</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G60" s="7"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
-        <v>7501</v>
+        <v>7304</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>25</v>
@@ -1921,16 +1931,16 @@
         <v>1</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G61" s="7"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
-        <v>7502</v>
+        <v>7401</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>25</v>
@@ -1942,16 +1952,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G62" s="7"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
-        <v>7503</v>
+        <v>7402</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>25</v>
@@ -1963,16 +1973,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G63" s="7"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
-        <v>7504</v>
+        <v>7403</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>25</v>
@@ -1984,16 +1994,16 @@
         <v>1</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G64" s="7"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
-        <v>7601</v>
+        <v>7404</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>25</v>
@@ -2005,16 +2015,16 @@
         <v>1</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G65" s="7"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
-        <v>7602</v>
+        <v>7501</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>25</v>
@@ -2026,16 +2036,16 @@
         <v>1</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G66" s="7"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
-        <v>7603</v>
+        <v>7502</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>25</v>
@@ -2047,16 +2057,16 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G67" s="7"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
-        <v>7604</v>
+        <v>7503</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>25</v>
@@ -2068,16 +2078,16 @@
         <v>1</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G68" s="7"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
-        <v>7701</v>
+        <v>7504</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>25</v>
@@ -2089,16 +2099,16 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G69" s="7"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
-        <v>7702</v>
+        <v>7601</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>25</v>
@@ -2110,16 +2120,16 @@
         <v>1</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
-        <v>7703</v>
+        <v>7602</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>25</v>
@@ -2131,142 +2141,142 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G71" s="7"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
+        <v>7603</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" s="7"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="7">
+        <v>7604</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" s="7"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="7">
+        <v>7701</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74" s="7"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="7">
+        <v>7702</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="7"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="7">
+        <v>7703</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="7"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="7">
         <v>7704</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D72" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="7" t="s">
+      <c r="B77" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F77" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G72" s="7"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="8">
-        <v>8101</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D73" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G73" s="8"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="8">
-        <v>8102</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D74" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="8"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="8">
-        <v>8103</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D75" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G75" s="8"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="8">
-        <v>8104</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G76" s="8"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="8">
-        <v>8201</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G77" s="8"/>
+      <c r="G77" s="7"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
-        <v>8202</v>
+        <v>8101</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>26</v>
@@ -2278,16 +2288,16 @@
         <v>1</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G78" s="8"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
-        <v>8203</v>
+        <v>8102</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>26</v>
@@ -2299,16 +2309,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G79" s="8"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
-        <v>8204</v>
+        <v>8103</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>26</v>
@@ -2320,16 +2330,16 @@
         <v>1</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
-        <v>8301</v>
+        <v>8104</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>26</v>
@@ -2341,16 +2351,16 @@
         <v>1</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G81" s="8"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
-        <v>8302</v>
+        <v>8201</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>26</v>
@@ -2362,16 +2372,16 @@
         <v>1</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G82" s="8"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
-        <v>8303</v>
+        <v>8202</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>26</v>
@@ -2383,16 +2393,16 @@
         <v>1</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G83" s="8"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
-        <v>8304</v>
+        <v>8203</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>26</v>
@@ -2404,16 +2414,16 @@
         <v>1</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G84" s="8"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
-        <v>8401</v>
+        <v>8204</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>26</v>
@@ -2425,16 +2435,16 @@
         <v>1</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G85" s="8"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
-        <v>8402</v>
+        <v>8301</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>26</v>
@@ -2446,16 +2456,16 @@
         <v>1</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G86" s="8"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
-        <v>8403</v>
+        <v>8302</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>26</v>
@@ -2467,16 +2477,16 @@
         <v>1</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G87" s="8"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
-        <v>8404</v>
+        <v>8303</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>26</v>
@@ -2488,16 +2498,16 @@
         <v>1</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G88" s="8"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
-        <v>8501</v>
+        <v>8304</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>26</v>
@@ -2509,16 +2519,16 @@
         <v>1</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
-        <v>8502</v>
+        <v>8401</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>26</v>
@@ -2530,16 +2540,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
-        <v>8503</v>
+        <v>8402</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>26</v>
@@ -2551,16 +2561,16 @@
         <v>1</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
-        <v>8504</v>
+        <v>8403</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>26</v>
@@ -2572,16 +2582,16 @@
         <v>1</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
-        <v>8601</v>
+        <v>8404</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>26</v>
@@ -2593,16 +2603,16 @@
         <v>1</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
-        <v>8602</v>
+        <v>8501</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>26</v>
@@ -2614,16 +2624,16 @@
         <v>1</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
-        <v>8603</v>
+        <v>8502</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>26</v>
@@ -2635,16 +2645,16 @@
         <v>1</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
-        <v>8604</v>
+        <v>8503</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>26</v>
@@ -2656,16 +2666,16 @@
         <v>1</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
-        <v>8701</v>
+        <v>8504</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>26</v>
@@ -2677,16 +2687,16 @@
         <v>1</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G97" s="8"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
-        <v>8702</v>
+        <v>8601</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>26</v>
@@ -2698,16 +2708,16 @@
         <v>1</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G98" s="8"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
-        <v>8703</v>
+        <v>8602</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>26</v>
@@ -2719,33 +2729,138 @@
         <v>1</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G99" s="8"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
+        <v>8603</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" s="8"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="8">
+        <v>8604</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D101" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="8"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="8">
+        <v>8701</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D102" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G102" s="8"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="8">
+        <v>8702</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D103" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="8"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="8">
+        <v>8703</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D104" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G104" s="8"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="8">
         <v>8704</v>
       </c>
-      <c r="B100" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D100" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" s="8" t="s">
+      <c r="B105" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F105" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G100" s="8"/>
+      <c r="G105" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data/Item.xlsx
+++ b/Data/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E778FD-84AE-48E9-BE80-41D22881EC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BE277C-9B42-4C03-8E3F-4918CAD7E2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="32">
   <si>
     <t>ItemId</t>
   </si>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="9" style="2"/>
@@ -584,7 +584,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -676,7 +676,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -768,7 +768,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -814,7 +814,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>6</v>
@@ -860,7 +860,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>6</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>1999</v>
+        <v>1014</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>6</v>
@@ -928,31 +928,31 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>2001</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="A17" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>8</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>8</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>8</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>8</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>8</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>8</v>
@@ -1135,31 +1135,31 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>3111</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="A26" s="3">
+        <v>2009</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>3121</v>
+        <v>3111</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>27</v>
@@ -1177,12 +1177,12 @@
         <v>20</v>
       </c>
       <c r="G27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>3131</v>
+        <v>3121</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>27</v>
@@ -1200,12 +1200,12 @@
         <v>20</v>
       </c>
       <c r="G28" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>3141</v>
+        <v>3131</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>27</v>
@@ -1223,12 +1223,12 @@
         <v>20</v>
       </c>
       <c r="G29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>3151</v>
+        <v>3141</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>27</v>
@@ -1246,12 +1246,12 @@
         <v>20</v>
       </c>
       <c r="G30" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>3161</v>
+        <v>3151</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>27</v>
@@ -1269,12 +1269,12 @@
         <v>20</v>
       </c>
       <c r="G31" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>3211</v>
+        <v>3161</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>27</v>
@@ -1286,21 +1286,21 @@
         <v>0</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G32" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>3221</v>
+        <v>3211</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>11</v>
@@ -1315,12 +1315,12 @@
         <v>20</v>
       </c>
       <c r="G33" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>3231</v>
+        <v>3221</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>28</v>
@@ -1338,12 +1338,12 @@
         <v>20</v>
       </c>
       <c r="G34" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>3241</v>
+        <v>3231</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>28</v>
@@ -1361,12 +1361,12 @@
         <v>20</v>
       </c>
       <c r="G35" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>3251</v>
+        <v>3241</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>28</v>
@@ -1384,12 +1384,12 @@
         <v>20</v>
       </c>
       <c r="G36" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>3261</v>
+        <v>3251</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>28</v>
@@ -1407,12 +1407,12 @@
         <v>20</v>
       </c>
       <c r="G37" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>3311</v>
+        <v>3261</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>28</v>
@@ -1424,18 +1424,18 @@
         <v>0</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G38" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>3321</v>
+        <v>3311</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>28</v>
@@ -1453,12 +1453,12 @@
         <v>20</v>
       </c>
       <c r="G39" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>3331</v>
+        <v>3321</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>28</v>
@@ -1476,12 +1476,12 @@
         <v>20</v>
       </c>
       <c r="G40" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>3341</v>
+        <v>3331</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>28</v>
@@ -1499,12 +1499,12 @@
         <v>20</v>
       </c>
       <c r="G41" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>3351</v>
+        <v>3341</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>28</v>
@@ -1522,12 +1522,12 @@
         <v>20</v>
       </c>
       <c r="G42" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>3361</v>
+        <v>3351</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>28</v>
@@ -1545,35 +1545,35 @@
         <v>20</v>
       </c>
       <c r="G43" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>3361</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="4">
         <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
-        <v>5001</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="5">
-        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>10</v>
@@ -1595,31 +1595,31 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="6">
-        <v>6001</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="A46" s="5">
+        <v>5002</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="6">
+      <c r="C46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>10</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>10</v>
@@ -1687,29 +1687,31 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
-        <v>7101</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" s="7"/>
+      <c r="A50" s="6">
+        <v>6004</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
-        <v>7102</v>
+        <v>7101</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>25</v>
@@ -1724,13 +1726,13 @@
         <v>7</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>25</v>
@@ -1745,13 +1747,13 @@
         <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G52" s="7"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>25</v>
@@ -1766,13 +1768,13 @@
         <v>7</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
-        <v>7201</v>
+        <v>7104</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>25</v>
@@ -1784,16 +1786,16 @@
         <v>1</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G54" s="7"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
-        <v>7202</v>
+        <v>7201</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>25</v>
@@ -1808,13 +1810,13 @@
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
-        <v>7203</v>
+        <v>7202</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>25</v>
@@ -1829,13 +1831,13 @@
         <v>12</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G56" s="7"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>7204</v>
+        <v>7203</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>25</v>
@@ -1850,13 +1852,13 @@
         <v>12</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G57" s="7"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
-        <v>7301</v>
+        <v>7204</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>25</v>
@@ -1868,16 +1870,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G58" s="7"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
-        <v>7302</v>
+        <v>7301</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>25</v>
@@ -1892,13 +1894,13 @@
         <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G59" s="7"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
-        <v>7303</v>
+        <v>7302</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>25</v>
@@ -1913,13 +1915,13 @@
         <v>13</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G60" s="7"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
-        <v>7304</v>
+        <v>7303</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>25</v>
@@ -1934,13 +1936,13 @@
         <v>13</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G61" s="7"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
-        <v>7401</v>
+        <v>7304</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>25</v>
@@ -1952,16 +1954,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G62" s="7"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
-        <v>7402</v>
+        <v>7401</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>25</v>
@@ -1976,13 +1978,13 @@
         <v>9</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G63" s="7"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
-        <v>7403</v>
+        <v>7402</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>25</v>
@@ -1997,13 +1999,13 @@
         <v>9</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" s="7"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
-        <v>7404</v>
+        <v>7403</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>25</v>
@@ -2018,13 +2020,13 @@
         <v>9</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G65" s="7"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
-        <v>7501</v>
+        <v>7404</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>25</v>
@@ -2036,16 +2038,16 @@
         <v>1</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G66" s="7"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
-        <v>7502</v>
+        <v>7501</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>25</v>
@@ -2060,13 +2062,13 @@
         <v>14</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G67" s="7"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
-        <v>7503</v>
+        <v>7502</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>25</v>
@@ -2081,13 +2083,13 @@
         <v>14</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G68" s="7"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
-        <v>7504</v>
+        <v>7503</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>25</v>
@@ -2102,13 +2104,13 @@
         <v>14</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G69" s="7"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
-        <v>7601</v>
+        <v>7504</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>25</v>
@@ -2120,16 +2122,16 @@
         <v>1</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
-        <v>7602</v>
+        <v>7601</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>25</v>
@@ -2144,13 +2146,13 @@
         <v>15</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G71" s="7"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
-        <v>7603</v>
+        <v>7602</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>25</v>
@@ -2165,13 +2167,13 @@
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
-        <v>7604</v>
+        <v>7603</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>25</v>
@@ -2186,13 +2188,13 @@
         <v>15</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G73" s="7"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
-        <v>7701</v>
+        <v>7604</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>25</v>
@@ -2204,16 +2206,16 @@
         <v>1</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G74" s="7"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
-        <v>7702</v>
+        <v>7701</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>25</v>
@@ -2228,13 +2230,13 @@
         <v>16</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G75" s="7"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
-        <v>7703</v>
+        <v>7702</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>25</v>
@@ -2249,13 +2251,13 @@
         <v>16</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G76" s="7"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
-        <v>7704</v>
+        <v>7703</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>25</v>
@@ -2270,34 +2272,34 @@
         <v>16</v>
       </c>
       <c r="F77" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="7"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="7">
+        <v>7704</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G77" s="7"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="8">
-        <v>8101</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D78" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" s="8"/>
+      <c r="G78" s="7"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>26</v>
@@ -2312,13 +2314,13 @@
         <v>7</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G79" s="8"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>26</v>
@@ -2333,13 +2335,13 @@
         <v>7</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>26</v>
@@ -2354,13 +2356,13 @@
         <v>7</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G81" s="8"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
-        <v>8201</v>
+        <v>8104</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>26</v>
@@ -2372,16 +2374,16 @@
         <v>1</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G82" s="8"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>26</v>
@@ -2396,13 +2398,13 @@
         <v>12</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G83" s="8"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>26</v>
@@ -2417,13 +2419,13 @@
         <v>12</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G84" s="8"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>26</v>
@@ -2438,13 +2440,13 @@
         <v>12</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G85" s="8"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
-        <v>8301</v>
+        <v>8204</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>26</v>
@@ -2456,16 +2458,16 @@
         <v>1</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G86" s="8"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
-        <v>8302</v>
+        <v>8301</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>26</v>
@@ -2480,13 +2482,13 @@
         <v>13</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G87" s="8"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
-        <v>8303</v>
+        <v>8302</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>26</v>
@@ -2501,13 +2503,13 @@
         <v>13</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G88" s="8"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
-        <v>8304</v>
+        <v>8303</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>26</v>
@@ -2522,13 +2524,13 @@
         <v>13</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
-        <v>8401</v>
+        <v>8304</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>26</v>
@@ -2540,16 +2542,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
-        <v>8402</v>
+        <v>8401</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>26</v>
@@ -2564,13 +2566,13 @@
         <v>9</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
-        <v>8403</v>
+        <v>8402</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>26</v>
@@ -2585,13 +2587,13 @@
         <v>9</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
-        <v>8404</v>
+        <v>8403</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>26</v>
@@ -2606,13 +2608,13 @@
         <v>9</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
-        <v>8501</v>
+        <v>8404</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>26</v>
@@ -2624,16 +2626,16 @@
         <v>1</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
-        <v>8502</v>
+        <v>8501</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>26</v>
@@ -2648,13 +2650,13 @@
         <v>14</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
-        <v>8503</v>
+        <v>8502</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>26</v>
@@ -2669,13 +2671,13 @@
         <v>14</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
-        <v>8504</v>
+        <v>8503</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>26</v>
@@ -2690,13 +2692,13 @@
         <v>14</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G97" s="8"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
-        <v>8601</v>
+        <v>8504</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>26</v>
@@ -2708,16 +2710,16 @@
         <v>1</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G98" s="8"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
-        <v>8602</v>
+        <v>8601</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>26</v>
@@ -2732,13 +2734,13 @@
         <v>15</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G99" s="8"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
-        <v>8603</v>
+        <v>8602</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>26</v>
@@ -2753,13 +2755,13 @@
         <v>15</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G100" s="8"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
-        <v>8604</v>
+        <v>8603</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>26</v>
@@ -2774,13 +2776,13 @@
         <v>15</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G101" s="8"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
-        <v>8701</v>
+        <v>8604</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>26</v>
@@ -2792,16 +2794,16 @@
         <v>1</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G102" s="8"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
-        <v>8702</v>
+        <v>8701</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>26</v>
@@ -2816,13 +2818,13 @@
         <v>16</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G103" s="8"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
-        <v>8703</v>
+        <v>8702</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>26</v>
@@ -2837,13 +2839,13 @@
         <v>16</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G104" s="8"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
-        <v>8704</v>
+        <v>8703</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>26</v>
@@ -2858,9 +2860,30 @@
         <v>16</v>
       </c>
       <c r="F105" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" s="8"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="8">
+        <v>8704</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G105" s="8"/>
+      <c r="G106" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
